--- a/src/online_retail/Segmented_customers.xlsx
+++ b/src/online_retail/Segmented_customers.xlsx
@@ -462,16 +462,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1571</v>
+        <v>1553</v>
       </c>
       <c r="C2" t="n">
-        <v>457.1845957988542</v>
+        <v>455.8615582743078</v>
       </c>
       <c r="D2" t="n">
-        <v>1.289624443029917</v>
+        <v>1.291693496458467</v>
       </c>
       <c r="E2" t="n">
-        <v>341.8424003819223</v>
+        <v>334.9166844816484</v>
       </c>
     </row>
     <row r="3">
@@ -481,16 +481,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1358</v>
+        <v>1341</v>
       </c>
       <c r="C3" t="n">
-        <v>61.2319587628866</v>
+        <v>60.84787472035794</v>
       </c>
       <c r="D3" t="n">
-        <v>2.152430044182621</v>
+        <v>2.167785234899329</v>
       </c>
       <c r="E3" t="n">
-        <v>537.7966730486008</v>
+        <v>527.7155495898584</v>
       </c>
     </row>
     <row r="4">
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1271</v>
+        <v>1254</v>
       </c>
       <c r="C4" t="n">
-        <v>19.15184893784422</v>
+        <v>18.68181818181818</v>
       </c>
       <c r="D4" t="n">
-        <v>17.36113296616837</v>
+        <v>17.44019138755981</v>
       </c>
       <c r="E4" t="n">
-        <v>9490.649476789929</v>
+        <v>9209.962109250398</v>
       </c>
     </row>
     <row r="5">
@@ -519,16 +519,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>689</v>
+        <v>682</v>
       </c>
       <c r="C5" t="n">
-        <v>235.3033381712627</v>
+        <v>230.741935483871</v>
       </c>
       <c r="D5" t="n">
-        <v>4.946298984034833</v>
+        <v>4.979472140762463</v>
       </c>
       <c r="E5" t="n">
-        <v>3347.408222060958</v>
+        <v>2721.736326979472</v>
       </c>
     </row>
     <row r="6">
@@ -538,16 +538,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>606</v>
+        <v>616</v>
       </c>
       <c r="C6" t="n">
-        <v>85.72277227722772</v>
+        <v>83.69642857142857</v>
       </c>
       <c r="D6" t="n">
-        <v>8.349834983498349</v>
+        <v>8.441558441558442</v>
       </c>
       <c r="E6" t="n">
-        <v>2988.39454620462</v>
+        <v>2949.247053571429</v>
       </c>
     </row>
     <row r="7">
@@ -557,16 +557,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="C7" t="n">
-        <v>368.4844559585492</v>
+        <v>365.9181585677749</v>
       </c>
       <c r="D7" t="n">
-        <v>3.865284974093264</v>
+        <v>3.882352941176471</v>
       </c>
       <c r="E7" t="n">
-        <v>767.1503626943005</v>
+        <v>747.7892838874679</v>
       </c>
     </row>
   </sheetData>
